--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.7109375" customWidth="1" min="1" max="1"/>
@@ -891,24 +891,69 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v9.0</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>增强</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>三模式整合（🅰一键生成/🅱人机协作7步/🅲调优一次性不打断）；10阶段调优流程；调优规则前置进生成规则（生成即达标）；新增诊断脚本 scripts/analyze_syllabus.py；质量标准11维度达标基准；必问确认清单Q1-Q3；反向提示词32→44条；组装前检查清单扩充。注：本行于 v9.1 发布时补记（v9.0 当日漏更 changelog）。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>44条</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>v9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>当前最新版本：v8.0 | 发布日期：2026-05-22 | 反向提示词：32条 | 空白模板：v8 | GitHub: https://github.com/mokch556-stack/ft-kecheng-kaifa</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="11" t="n"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>v9.1</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>当前最新版本：v9.1 | 发布日期：2026-09-04 | 反向提示词：49条 | 空白模板：v9 | GitHub: https://github.com/mokch556-stack/ft-kecheng-kaifa</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
